--- a/analysis/experiment_analysis.xlsx
+++ b/analysis/experiment_analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\Desktop\Business Analytics with Gen AI\Capstone Project\Part 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABEF5A4A-B86A-43B8-BB6F-DE98D14ED5BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA16FCD0-9CA5-4342-9FF2-396D2CDEC853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FECA3217-D8C2-4582-9DD0-CCEDEC4561C1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="43">
   <si>
     <t>Control</t>
   </si>
@@ -151,6 +151,9 @@
   </si>
   <si>
     <t>Average days to convert</t>
+  </si>
+  <si>
+    <t>Task 5: Create Experiment Summary</t>
   </si>
 </sst>
 </file>
@@ -642,10 +645,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B92358F0-DC0E-4952-A5F4-D1E2E1110158}">
-  <dimension ref="B4:O72"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="41.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.33203125" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="12.21875" customWidth="1"/>
     <col min="8" max="8" width="27.44140625" bestFit="1" customWidth="1"/>
@@ -653,7 +656,13 @@
     <col min="13" max="13" width="11.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:15" ht="18.600000000000001">
+    <row r="1" spans="1:15" ht="18.600000000000001">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1"/>
+    </row>
+    <row r="4" spans="1:15" ht="18.600000000000001">
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
@@ -665,7 +674,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="5" spans="2:15" ht="16.8">
+    <row r="5" spans="1:15" ht="16.8">
       <c r="B5" s="5" t="s">
         <v>16</v>
       </c>
@@ -680,7 +689,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="2:15">
+    <row r="7" spans="1:15">
       <c r="B7" s="4"/>
       <c r="C7" s="6" t="s">
         <v>19</v>
@@ -714,7 +723,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="2:15">
+    <row r="8" spans="1:15">
       <c r="B8" s="6" t="s">
         <v>0</v>
       </c>
@@ -760,7 +769,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="9" spans="2:15">
+    <row r="9" spans="1:15">
       <c r="B9" s="6" t="s">
         <v>13</v>
       </c>
@@ -806,7 +815,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="11" spans="2:15" ht="16.8">
+    <row r="11" spans="1:15" ht="16.8">
       <c r="B11" s="5" t="s">
         <v>23</v>
       </c>
@@ -814,7 +823,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:15">
+    <row r="13" spans="1:15">
       <c r="B13" s="4"/>
       <c r="C13" s="6" t="s">
         <v>1</v>
@@ -842,7 +851,7 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
     </row>
-    <row r="14" spans="2:15">
+    <row r="14" spans="1:15">
       <c r="B14" s="6" t="s">
         <v>0</v>
       </c>
@@ -881,7 +890,7 @@
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
     </row>
-    <row r="15" spans="2:15">
+    <row r="15" spans="1:15">
       <c r="B15" s="6" t="s">
         <v>13</v>
       </c>
